--- a/templates/색인목록(서식).xlsx
+++ b/templates/색인목록(서식).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\엑셀매크로\나)기록물관리시스템 및 이관신청서자동화\서식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C87D13E-5E7D-493C-82D6-907BF9E3F69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B489FBE-B77D-4BC4-A54B-6B39DEE9E398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" xr2:uid="{C20A73D0-3232-4490-AC52-F904F9C03FA4}"/>
+    <workbookView xWindow="1215" yWindow="570" windowWidth="24855" windowHeight="15420" xr2:uid="{C20A73D0-3232-4490-AC52-F904F9C03FA4}"/>
   </bookViews>
   <sheets>
     <sheet name="색인목록(서식)" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -167,6 +167,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -176,36 +185,39 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -506,340 +518,360 @@
   <sheetData>
     <row r="1" spans="1:11" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="11.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="B4" s="8"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
     </row>
     <row r="26" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
     </row>
     <row r="27" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
@@ -847,26 +879,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0" right="0.17" top="0" bottom="0" header="0" footer="0"/>

--- a/templates/색인목록(서식).xlsx
+++ b/templates/색인목록(서식).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\엑셀매크로\나)기록물관리시스템 및 이관신청서자동화\서식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B489FBE-B77D-4BC4-A54B-6B39DEE9E398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60230AF6-CC4C-449E-BC10-180C83B853CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="570" windowWidth="24855" windowHeight="15420" xr2:uid="{C20A73D0-3232-4490-AC52-F904F9C03FA4}"/>
+    <workbookView xWindow="3945" yWindow="780" windowWidth="24855" windowHeight="15420" xr2:uid="{C20A73D0-3232-4490-AC52-F904F9C03FA4}"/>
   </bookViews>
   <sheets>
     <sheet name="색인목록(서식)" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -202,6 +202,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -518,40 +521,40 @@
   <sheetData>
     <row r="1" spans="1:11" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="11.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
@@ -576,8 +579,8 @@
     </row>
     <row r="6" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -588,8 +591,8 @@
     </row>
     <row r="7" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -600,8 +603,8 @@
     </row>
     <row r="8" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -612,8 +615,8 @@
     </row>
     <row r="9" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -624,8 +627,8 @@
     </row>
     <row r="10" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -636,8 +639,8 @@
     </row>
     <row r="11" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -648,8 +651,8 @@
     </row>
     <row r="12" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -660,8 +663,8 @@
     </row>
     <row r="13" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -672,8 +675,8 @@
     </row>
     <row r="14" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -684,8 +687,8 @@
     </row>
     <row r="15" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -696,8 +699,8 @@
     </row>
     <row r="16" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -708,8 +711,8 @@
     </row>
     <row r="17" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -720,8 +723,8 @@
     </row>
     <row r="18" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -732,8 +735,8 @@
     </row>
     <row r="19" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -744,8 +747,8 @@
     </row>
     <row r="20" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -756,8 +759,8 @@
     </row>
     <row r="21" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -768,8 +771,8 @@
     </row>
     <row r="22" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -780,8 +783,8 @@
     </row>
     <row r="23" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -792,8 +795,8 @@
     </row>
     <row r="24" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -804,8 +807,8 @@
     </row>
     <row r="25" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -816,8 +819,8 @@
     </row>
     <row r="26" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -828,8 +831,8 @@
     </row>
     <row r="27" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -840,8 +843,8 @@
     </row>
     <row r="28" spans="1:10" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -852,26 +855,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
@@ -879,6 +862,26 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0" right="0.17" top="0" bottom="0" header="0" footer="0"/>
